--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.0463516949528</v>
+        <v>8.132532150429832</v>
       </c>
       <c r="D2" t="n">
-        <v>49.87257594942053</v>
+        <v>8.104293591780836</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F2" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.69474228366817</v>
+        <v>9.050395621096078</v>
       </c>
       <c r="D3" t="n">
-        <v>55.7487924092277</v>
+        <v>9.059178766499501</v>
       </c>
       <c r="E3" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F3" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.82173516198102</v>
+        <v>5.171031963821916</v>
       </c>
       <c r="D4" t="n">
-        <v>31.72780297981192</v>
+        <v>5.155767984219437</v>
       </c>
       <c r="E4" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F4" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.08352915850072</v>
+        <v>6.838573488256368</v>
       </c>
       <c r="D5" t="n">
-        <v>41.81491651887223</v>
+        <v>6.794923934316738</v>
       </c>
       <c r="E5" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F5" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.03270470433852</v>
+        <v>8.617814514455009</v>
       </c>
       <c r="D6" t="n">
-        <v>53.21605680112852</v>
+        <v>8.647609230183386</v>
       </c>
       <c r="E6" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F6" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.4395219038207</v>
+        <v>7.058922309370864</v>
       </c>
       <c r="D7" t="n">
-        <v>43.58714614570614</v>
+        <v>7.082911248677249</v>
       </c>
       <c r="E7" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F7" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.62114414532807</v>
+        <v>4.488435923615812</v>
       </c>
       <c r="D8" t="n">
-        <v>27.77381838062009</v>
+        <v>4.513245486850765</v>
       </c>
       <c r="E8" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F8" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.38788749645444</v>
+        <v>8.838031718173847</v>
       </c>
       <c r="D9" t="n">
-        <v>54.12989653042896</v>
+        <v>8.796108186194706</v>
       </c>
       <c r="E9" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F9" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.72728817224003</v>
+        <v>4.180684327989004</v>
       </c>
       <c r="D10" t="n">
-        <v>25.82684307097167</v>
+        <v>4.196861999032896</v>
       </c>
       <c r="E10" t="n">
-        <v>11.0598880554201</v>
+        <v>1.797231809005767</v>
       </c>
       <c r="F10" t="n">
-        <v>11.01695843323203</v>
+        <v>1.790255745400204</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
